--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>136420582</v>
       </c>
       <c r="B15" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>136420582</v>
       </c>
       <c r="B15" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>136420582</v>
       </c>
       <c r="B15" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136420049</v>
       </c>
       <c r="B49" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>136420324</v>
       </c>
       <c r="B50" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>136420582</v>
       </c>
       <c r="B15" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ107"/>
+  <dimension ref="A1:AZ109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6699,48 +6699,56 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118118723</v>
+        <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79946</v>
+        <v>79476</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>362344</v>
+        <v>363276</v>
       </c>
       <c r="R51" t="n">
-        <v>6882253</v>
+        <v>6883022</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6767,27 +6775,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Växer på stubbe av jättetall</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6796,19 +6799,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Fjällnära</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6824,16 +6816,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118723</t>
+          <t>https://artportalen.se/Sighting/136873109</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121898927</v>
+        <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>83305</v>
+        <v>79476</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6841,37 +6833,44 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>363129</v>
+        <v>363300</v>
       </c>
       <c r="R52" t="n">
-        <v>6882975</v>
+        <v>6882876</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6895,22 +6894,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6925,27 +6924,27 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121898927</t>
+          <t>https://artportalen.se/Sighting/136873218</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118103394</v>
+        <v>118118723</v>
       </c>
       <c r="B53" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6953,42 +6952,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>362272</v>
+        <v>362344</v>
       </c>
       <c r="R53" t="n">
-        <v>6882099</v>
+        <v>6882253</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7015,27 +7009,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska hacksmärken på gran Grannaturskog</t>
+          <t>Växer på stubbe av jättetall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7044,6 +7038,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7054,7 +7049,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Grannaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7071,62 +7066,54 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103394</t>
+          <t>https://artportalen.se/Sighting/118118723</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118103560</v>
+        <v>121898927</v>
       </c>
       <c r="B54" t="n">
-        <v>57953</v>
+        <v>83305</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>362276</v>
+        <v>363129</v>
       </c>
       <c r="R54" t="n">
-        <v>6882083</v>
+        <v>6882975</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7150,27 +7137,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på gran i grannaturskog som är avverkningsanmäld.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7181,38 +7163,28 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Grannaturskog</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118103560</t>
+          <t>https://artportalen.se/Sighting/121898927</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118107736</v>
+        <v>118103394</v>
       </c>
       <c r="B55" t="n">
         <v>57953</v>
@@ -7251,14 +7223,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>362349</v>
+        <v>362272</v>
       </c>
       <c r="R55" t="n">
-        <v>6882279</v>
+        <v>6882099</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7290,7 +7262,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7300,12 +7272,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i naturskog.</t>
+          <t>Färska hacksmärken på gran Grannaturskog</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7324,7 +7296,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Mycket gamla granar och tallar</t>
+          <t>Grannaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7341,13 +7313,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118107736</t>
+          <t>https://artportalen.se/Sighting/118103394</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118113015</v>
+        <v>118103560</v>
       </c>
       <c r="B56" t="n">
         <v>57953</v>
@@ -7375,16 +7347,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7394,10 +7362,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>362487</v>
+        <v>362276</v>
       </c>
       <c r="R56" t="n">
-        <v>6882179</v>
+        <v>6882083</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7424,27 +7392,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Hackmärken på gran i myrholme.</t>
+          <t>Färska hackmärken på gran i grannaturskog som är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7455,6 +7423,16 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Grannaturskog</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7470,13 +7448,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113015</t>
+          <t>https://artportalen.se/Sighting/118103560</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118113051</v>
+        <v>118107736</v>
       </c>
       <c r="B57" t="n">
         <v>57953</v>
@@ -7504,32 +7482,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>362482</v>
+        <v>362349</v>
       </c>
       <c r="R57" t="n">
-        <v>6882180</v>
+        <v>6882279</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7553,27 +7527,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Hackmärken gran på myrholme. Naturskog</t>
+          <t>Färska hackmärken på gran i naturskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7584,6 +7558,16 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Mycket gamla granar och tallar</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7599,13 +7583,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118113051</t>
+          <t>https://artportalen.se/Sighting/118107736</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118118450</v>
+        <v>118113015</v>
       </c>
       <c r="B58" t="n">
         <v>57953</v>
@@ -7633,12 +7617,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7648,10 +7636,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>362489</v>
+        <v>362487</v>
       </c>
       <c r="R58" t="n">
-        <v>6882203</v>
+        <v>6882179</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7683,7 +7671,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7693,12 +7681,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Hackmärken på gran. Myrholme som är avverkningsanmäld</t>
+          <t>Hackmärken på gran i myrholme.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7709,16 +7697,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Barrnaturskog. Lokalt fuktig miljö</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7734,13 +7712,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118450</t>
+          <t>https://artportalen.se/Sighting/118113015</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118118466</v>
+        <v>118113051</v>
       </c>
       <c r="B59" t="n">
         <v>57953</v>
@@ -7768,28 +7746,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>362421</v>
+        <v>362482</v>
       </c>
       <c r="R59" t="n">
-        <v>6882227</v>
+        <v>6882180</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7818,7 +7800,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7828,12 +7810,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska hackmärken på fertalet grannar på denna myrholme.</t>
+          <t>Hackmärken gran på myrholme. Naturskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7844,16 +7826,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Barrnaturskog på myrholme</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7869,13 +7841,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118466</t>
+          <t>https://artportalen.se/Sighting/118113051</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118118547</v>
+        <v>118118450</v>
       </c>
       <c r="B60" t="n">
         <v>57953</v>
@@ -7908,20 +7880,20 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>362378</v>
+        <v>362489</v>
       </c>
       <c r="R60" t="n">
-        <v>6882297</v>
+        <v>6882203</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7953,7 +7925,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7963,12 +7935,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre hackmärken på gammal gran i barrnaturskog.</t>
+          <t>Hackmärken på gran. Myrholme som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7987,7 +7959,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Lokalt fuktig miljö</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8004,13 +7976,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118547</t>
+          <t>https://artportalen.se/Sighting/118118450</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118118562</v>
+        <v>118118466</v>
       </c>
       <c r="B61" t="n">
         <v>57953</v>
@@ -8049,14 +8021,14 @@
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>362373</v>
+        <v>362421</v>
       </c>
       <c r="R61" t="n">
-        <v>6882312</v>
+        <v>6882227</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8088,7 +8060,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8098,12 +8070,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Hackmärken på gammal gran i barrnaturskog. Skogen är avverkningsanmäld</t>
+          <t>Färska hackmärken på fertalet grannar på denna myrholme.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8122,7 +8094,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog på myrholme</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8139,13 +8111,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118562</t>
+          <t>https://artportalen.se/Sighting/118118466</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118118603</v>
+        <v>118118547</v>
       </c>
       <c r="B62" t="n">
         <v>57953</v>
@@ -8178,20 +8150,20 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>362381</v>
+        <v>362378</v>
       </c>
       <c r="R62" t="n">
-        <v>6882250</v>
+        <v>6882297</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8223,7 +8195,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8233,12 +8205,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gammal gran i barrnaturskog som avverkningsanmäld.</t>
+          <t>Äldre hackmärken på gammal gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8257,7 +8229,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8274,13 +8246,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118603</t>
+          <t>https://artportalen.se/Sighting/118118547</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118118863</v>
+        <v>118118562</v>
       </c>
       <c r="B63" t="n">
         <v>57953</v>
@@ -8323,10 +8295,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>362327</v>
+        <v>362373</v>
       </c>
       <c r="R63" t="n">
-        <v>6882265</v>
+        <v>6882312</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8358,7 +8330,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8368,12 +8340,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog som är avverkningsanmäld</t>
+          <t>Hackmärken på gammal gran i barrnaturskog. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8409,13 +8381,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118863</t>
+          <t>https://artportalen.se/Sighting/118118562</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118118905</v>
+        <v>118118603</v>
       </c>
       <c r="B64" t="n">
         <v>57953</v>
@@ -8448,20 +8420,20 @@
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>362338</v>
+        <v>362381</v>
       </c>
       <c r="R64" t="n">
-        <v>6882298</v>
+        <v>6882250</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8508,7 +8480,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Hackmärken på gran i barrnaturskog</t>
+          <t>Färska hackmärken på gammal gran i barrnaturskog som avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8544,13 +8516,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118905</t>
+          <t>https://artportalen.se/Sighting/118118603</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118119133</v>
+        <v>118118863</v>
       </c>
       <c r="B65" t="n">
         <v>57953</v>
@@ -8593,10 +8565,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>362371</v>
+        <v>362327</v>
       </c>
       <c r="R65" t="n">
-        <v>6882362</v>
+        <v>6882265</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8628,7 +8600,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8638,12 +8610,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska hackmärken på grov gammal gran. i barrnaturskog som är hotad av avverkning.</t>
+          <t>Färska hackmärken på gran i barrnaturskog som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8679,13 +8651,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119133</t>
+          <t>https://artportalen.se/Sighting/118118863</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118119170</v>
+        <v>118118905</v>
       </c>
       <c r="B66" t="n">
         <v>57953</v>
@@ -8718,7 +8690,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -8728,10 +8700,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>362327</v>
+        <v>362338</v>
       </c>
       <c r="R66" t="n">
-        <v>6882360</v>
+        <v>6882298</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -8763,7 +8735,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8773,12 +8745,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Färska hackmärken på grov gammal gran i barrnaturskog. Avverkningsanmäld skog.</t>
+          <t>Hackmärken på gran i barrnaturskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8797,7 +8769,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Barrnatursk. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8814,13 +8786,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119170</t>
+          <t>https://artportalen.se/Sighting/118118905</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118119483</v>
+        <v>118119133</v>
       </c>
       <c r="B67" t="n">
         <v>57953</v>
@@ -8863,10 +8835,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>362284</v>
+        <v>362371</v>
       </c>
       <c r="R67" t="n">
-        <v>6882318</v>
+        <v>6882362</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8898,7 +8870,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8908,12 +8880,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog.</t>
+          <t>Färska hackmärken på grov gammal gran. i barrnaturskog som är hotad av avverkning.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8949,13 +8921,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119483</t>
+          <t>https://artportalen.se/Sighting/118119133</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118119653</v>
+        <v>118119170</v>
       </c>
       <c r="B68" t="n">
         <v>57953</v>
@@ -8988,7 +8960,7 @@
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8998,10 +8970,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>362269</v>
+        <v>362327</v>
       </c>
       <c r="R68" t="n">
-        <v>6882324</v>
+        <v>6882360</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -9033,7 +9005,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9043,12 +9015,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Hackmärken på grov gran intill skidspår som går genom barrnaturskogen. Avverkningsanmäld skog.</t>
+          <t>Färska hackmärken på grov gammal gran i barrnaturskog. Avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9067,7 +9039,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnatursk. Fjällnära</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9084,13 +9056,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119653</t>
+          <t>https://artportalen.se/Sighting/118119170</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118119701</v>
+        <v>118119483</v>
       </c>
       <c r="B69" t="n">
         <v>57953</v>
@@ -9133,10 +9105,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>362279</v>
+        <v>362284</v>
       </c>
       <c r="R69" t="n">
-        <v>6882363</v>
+        <v>6882318</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -9168,7 +9140,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9178,12 +9150,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog som hotas av avverkning</t>
+          <t>Färska hackmärken på gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9219,13 +9191,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119701</t>
+          <t>https://artportalen.se/Sighting/118119483</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118119770</v>
+        <v>118119653</v>
       </c>
       <c r="B70" t="n">
         <v>57953</v>
@@ -9258,7 +9230,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9268,10 +9240,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>362240</v>
+        <v>362269</v>
       </c>
       <c r="R70" t="n">
-        <v>6882345</v>
+        <v>6882324</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9318,7 +9290,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gammal gran i barrnaturskog.</t>
+          <t>Hackmärken på grov gran intill skidspår som går genom barrnaturskogen. Avverkningsanmäld skog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9354,13 +9326,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119770</t>
+          <t>https://artportalen.se/Sighting/118119653</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118119872</v>
+        <v>118119701</v>
       </c>
       <c r="B71" t="n">
         <v>57953</v>
@@ -9393,7 +9365,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9403,10 +9375,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>362230</v>
+        <v>362279</v>
       </c>
       <c r="R71" t="n">
-        <v>6882332</v>
+        <v>6882363</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9438,7 +9410,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9448,7 +9420,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran i barrnaturskog som hotas av avverkning</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9484,13 +9461,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119872</t>
+          <t>https://artportalen.se/Sighting/118119701</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118120074</v>
+        <v>118119770</v>
       </c>
       <c r="B72" t="n">
         <v>57953</v>
@@ -9533,10 +9510,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>362243</v>
+        <v>362240</v>
       </c>
       <c r="R72" t="n">
-        <v>6882254</v>
+        <v>6882345</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9568,7 +9545,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9578,12 +9555,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken på gammal gran i barrnatuskog.</t>
+          <t>Färska hackmärken på gammal gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9619,13 +9596,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120074</t>
+          <t>https://artportalen.se/Sighting/118119770</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118120164</v>
+        <v>118119872</v>
       </c>
       <c r="B73" t="n">
         <v>57953</v>
@@ -9658,7 +9635,7 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -9668,10 +9645,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>362252</v>
+        <v>362230</v>
       </c>
       <c r="R73" t="n">
-        <v>6882248</v>
+        <v>6882332</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9703,7 +9680,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9713,12 +9690,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska hackmärken på gran in barrnaturskog.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9754,13 +9726,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120164</t>
+          <t>https://artportalen.se/Sighting/118119872</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118120248</v>
+        <v>118120074</v>
       </c>
       <c r="B74" t="n">
         <v>57953</v>
@@ -9803,10 +9775,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>362267</v>
+        <v>362243</v>
       </c>
       <c r="R74" t="n">
-        <v>6882224</v>
+        <v>6882254</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9838,7 +9810,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9848,12 +9820,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska hackmärken i ett granbestånd. I avverkningsanmält skogsområe</t>
+          <t>Färska och äldre hackmärken på gammal gran i barrnatuskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9889,13 +9861,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120248</t>
+          <t>https://artportalen.se/Sighting/118120074</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118120388</v>
+        <v>118120164</v>
       </c>
       <c r="B75" t="n">
         <v>57953</v>
@@ -9928,7 +9900,7 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
@@ -9938,10 +9910,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>362196</v>
+        <v>362252</v>
       </c>
       <c r="R75" t="n">
-        <v>6882301</v>
+        <v>6882248</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9986,6 +9958,11 @@
           <t>15:30</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska hackmärken på gran in barrnaturskog.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -10002,7 +9979,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10019,13 +9996,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120388</t>
+          <t>https://artportalen.se/Sighting/118120164</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118120447</v>
+        <v>118120248</v>
       </c>
       <c r="B76" t="n">
         <v>57953</v>
@@ -10068,10 +10045,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>362200</v>
+        <v>362267</v>
       </c>
       <c r="R76" t="n">
-        <v>6882350</v>
+        <v>6882224</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -10103,7 +10080,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10113,12 +10090,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken på grov gran i barrnaturskog.</t>
+          <t>Färska hackmärken i ett granbestånd. I avverkningsanmält skogsområe</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10154,13 +10131,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120447</t>
+          <t>https://artportalen.se/Sighting/118120248</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118120506</v>
+        <v>118120388</v>
       </c>
       <c r="B77" t="n">
         <v>57953</v>
@@ -10203,10 +10180,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>362168</v>
+        <v>362196</v>
       </c>
       <c r="R77" t="n">
-        <v>6882359</v>
+        <v>6882301</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10238,7 +10215,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10248,12 +10225,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre hackmärken på gammal gran med garnlav. I avverkningsanmäld barrnaturskog</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10272,7 +10244,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Barrnaturskog.</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10289,13 +10261,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118120506</t>
+          <t>https://artportalen.se/Sighting/118120388</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118122341</v>
+        <v>118120447</v>
       </c>
       <c r="B78" t="n">
         <v>57953</v>
@@ -10334,14 +10306,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>362247</v>
+        <v>362200</v>
       </c>
       <c r="R78" t="n">
-        <v>6882178</v>
+        <v>6882350</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -10368,27 +10340,27 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Hackmärken på tall i barrnaturskog.</t>
+          <t>Färska och äldre hackmärken på grov gran i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10407,7 +10379,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -10424,13 +10396,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122341</t>
+          <t>https://artportalen.se/Sighting/118120447</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118122435</v>
+        <v>118120506</v>
       </c>
       <c r="B79" t="n">
         <v>57953</v>
@@ -10463,20 +10435,20 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>362276</v>
+        <v>362168</v>
       </c>
       <c r="R79" t="n">
-        <v>6882136</v>
+        <v>6882359</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10503,27 +10475,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i barrnaturskog</t>
+          <t>Äldre hackmärken på gammal gran med garnlav. I avverkningsanmäld barrnaturskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10542,7 +10514,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Barrnaturskog.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -10559,13 +10531,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122435</t>
+          <t>https://artportalen.se/Sighting/118120506</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118122458</v>
+        <v>118122341</v>
       </c>
       <c r="B80" t="n">
         <v>57953</v>
@@ -10608,10 +10580,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>362281</v>
+        <v>362247</v>
       </c>
       <c r="R80" t="n">
-        <v>6882135</v>
+        <v>6882178</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10643,7 +10615,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10653,12 +10625,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fin barrnaturskog som är avverkningsanmäld</t>
+          <t>Hackmärken på tall i barrnaturskog.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10694,13 +10666,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122458</t>
+          <t>https://artportalen.se/Sighting/118122341</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118122497</v>
+        <v>118122435</v>
       </c>
       <c r="B81" t="n">
         <v>57953</v>
@@ -10743,10 +10715,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>362283</v>
+        <v>362276</v>
       </c>
       <c r="R81" t="n">
-        <v>6882105</v>
+        <v>6882136</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -10778,7 +10750,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10788,12 +10760,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i avverkningsanmäld barrnaturskog</t>
+          <t>Färska hackmärken på gran i barrnaturskog</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10829,13 +10801,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122497</t>
+          <t>https://artportalen.se/Sighting/118122435</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118340481</v>
+        <v>118122458</v>
       </c>
       <c r="B82" t="n">
         <v>57953</v>
@@ -10878,10 +10850,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>362275</v>
+        <v>362281</v>
       </c>
       <c r="R82" t="n">
-        <v>6882133</v>
+        <v>6882135</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10908,27 +10880,27 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog.</t>
+          <t>Färska hackmärken på gran i fin barrnaturskog som är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10947,7 +10919,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -10964,13 +10936,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340481</t>
+          <t>https://artportalen.se/Sighting/118122458</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118340595</v>
+        <v>118122497</v>
       </c>
       <c r="B83" t="n">
         <v>57953</v>
@@ -11013,10 +10985,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>362281</v>
+        <v>362283</v>
       </c>
       <c r="R83" t="n">
-        <v>6882106</v>
+        <v>6882105</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -11043,27 +11015,27 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>färska hackmärken på gatan. Fjällnära skog</t>
+          <t>Färska hackmärken på gran i avverkningsanmäld barrnaturskog</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11082,7 +11054,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11099,13 +11071,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340595</t>
+          <t>https://artportalen.se/Sighting/118122497</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118340691</v>
+        <v>118340481</v>
       </c>
       <c r="B84" t="n">
         <v>57953</v>
@@ -11148,13 +11120,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>362270</v>
+        <v>362275</v>
       </c>
       <c r="R84" t="n">
-        <v>6882100</v>
+        <v>6882133</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11198,7 +11170,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska hackmärken på gran i fjällnära skog</t>
+          <t>Färska hackmärken på gran i fjällnära skog.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11234,13 +11206,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340691</t>
+          <t>https://artportalen.se/Sighting/118340481</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118340748</v>
+        <v>118340595</v>
       </c>
       <c r="B85" t="n">
         <v>57953</v>
@@ -11283,10 +11255,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>362272</v>
+        <v>362281</v>
       </c>
       <c r="R85" t="n">
-        <v>6882086</v>
+        <v>6882106</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -11333,7 +11305,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>färska hackmnärken på gran i naturskog. Fjällnära</t>
+          <t>färska hackmärken på gatan. Fjällnära skog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11369,13 +11341,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340748</t>
+          <t>https://artportalen.se/Sighting/118340595</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118340920</v>
+        <v>118340691</v>
       </c>
       <c r="B86" t="n">
         <v>57953</v>
@@ -11414,17 +11386,17 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>362284</v>
+        <v>362270</v>
       </c>
       <c r="R86" t="n">
-        <v>6882361</v>
+        <v>6882100</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11468,7 +11440,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
+          <t>Färska hackmärken på gran i fjällnära skog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11487,7 +11459,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -11504,13 +11476,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118340920</t>
+          <t>https://artportalen.se/Sighting/118340691</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121206319</v>
+        <v>118340748</v>
       </c>
       <c r="B87" t="n">
         <v>57953</v>
@@ -11539,19 +11511,27 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>363246</v>
+        <v>362272</v>
       </c>
       <c r="R87" t="n">
-        <v>6883004</v>
+        <v>6882086</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11575,22 +11555,27 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>färska hackmnärken på gran i naturskog. Fjällnära</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11601,28 +11586,38 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206319</t>
+          <t>https://artportalen.se/Sighting/118340748</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127170971</v>
+        <v>118340920</v>
       </c>
       <c r="B88" t="n">
         <v>57953</v>
@@ -11650,32 +11645,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>363315</v>
+        <v>362284</v>
       </c>
       <c r="R88" t="n">
-        <v>6882898</v>
+        <v>6882361</v>
       </c>
       <c r="S88" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11699,22 +11690,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken. Skogen är avverkningsanmäld. Gran med hackmärken inom anmälan. Se bild</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11725,6 +11721,16 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11740,13 +11746,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127170971</t>
+          <t>https://artportalen.se/Sighting/118340920</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127172142</v>
+        <v>121206319</v>
       </c>
       <c r="B89" t="n">
         <v>57953</v>
@@ -11774,32 +11780,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>363196</v>
+        <v>363246</v>
       </c>
       <c r="R89" t="n">
-        <v>6882950</v>
+        <v>6883004</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11823,27 +11817,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackmärken.</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11858,24 +11847,24 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172142</t>
+          <t>https://artportalen.se/Sighting/121206319</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127172737</v>
+        <v>127170971</v>
       </c>
       <c r="B90" t="n">
         <v>57953</v>
@@ -11922,10 +11911,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>363143</v>
+        <v>363315</v>
       </c>
       <c r="R90" t="n">
-        <v>6882797</v>
+        <v>6882898</v>
       </c>
       <c r="S90" t="n">
         <v>4</v>
@@ -11957,7 +11946,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11967,7 +11956,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11993,13 +11982,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172737</t>
+          <t>https://artportalen.se/Sighting/127170971</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127172795</v>
+        <v>127172142</v>
       </c>
       <c r="B91" t="n">
         <v>57953</v>
@@ -12046,13 +12035,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>363188</v>
+        <v>363196</v>
       </c>
       <c r="R91" t="n">
-        <v>6882809</v>
+        <v>6882950</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12081,7 +12070,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12091,12 +12080,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Färska och äldre hackmärken</t>
+          <t>Färska och äldre hackmärken.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12122,13 +12111,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172795</t>
+          <t>https://artportalen.se/Sighting/127172142</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127172899</v>
+        <v>127172737</v>
       </c>
       <c r="B92" t="n">
         <v>57953</v>
@@ -12175,13 +12164,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>363234</v>
+        <v>363143</v>
       </c>
       <c r="R92" t="n">
-        <v>6882800</v>
+        <v>6882797</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -12210,7 +12199,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -12220,7 +12209,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12246,13 +12235,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172899</t>
+          <t>https://artportalen.se/Sighting/127172737</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127315676</v>
+        <v>127172795</v>
       </c>
       <c r="B93" t="n">
         <v>57953</v>
@@ -12282,42 +12271,30 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>363122</v>
+        <v>363188</v>
       </c>
       <c r="R93" t="n">
-        <v>6882946</v>
+        <v>6882809</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -12341,22 +12318,27 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackmärken</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12371,24 +12353,24 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127315676</t>
+          <t>https://artportalen.se/Sighting/127172795</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128822185</v>
+        <v>127172899</v>
       </c>
       <c r="B94" t="n">
         <v>57953</v>
@@ -12428,24 +12410,20 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>362326</v>
+        <v>363234</v>
       </c>
       <c r="R94" t="n">
-        <v>6882768</v>
+        <v>6882800</v>
       </c>
       <c r="S94" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -12469,22 +12447,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12510,13 +12488,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822185</t>
+          <t>https://artportalen.se/Sighting/127172899</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128822490</v>
+        <v>127315676</v>
       </c>
       <c r="B95" t="n">
         <v>57953</v>
@@ -12546,14 +12524,22 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -12563,17 +12549,17 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>362260</v>
+        <v>363122</v>
       </c>
       <c r="R95" t="n">
-        <v>6882421</v>
+        <v>6882946</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12597,22 +12583,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12627,24 +12613,24 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822490</t>
+          <t>https://artportalen.se/Sighting/127315676</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128822499</v>
+        <v>128822185</v>
       </c>
       <c r="B96" t="n">
         <v>57953</v>
@@ -12684,20 +12670,24 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>362273</v>
+        <v>362326</v>
       </c>
       <c r="R96" t="n">
-        <v>6882421</v>
+        <v>6882768</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12726,7 +12716,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12736,7 +12726,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12762,63 +12752,70 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128822499</t>
+          <t>https://artportalen.se/Sighting/128822185</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118122325</v>
+        <v>128822490</v>
       </c>
       <c r="B97" t="n">
-        <v>5179</v>
+        <v>57953</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>362234</v>
+        <v>362260</v>
       </c>
       <c r="R97" t="n">
-        <v>6882185</v>
+        <v>6882421</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12842,27 +12839,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>På torrgran vid myrknat intill barrnaturskog</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12871,19 +12863,8 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>Myrmark intill barrnaturskog</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12899,16 +12880,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122325</t>
+          <t>https://artportalen.se/Sighting/128822490</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127315773</v>
+        <v>128822499</v>
       </c>
       <c r="B98" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12916,16 +12897,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -12935,37 +12916,30 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>363120</v>
+        <v>362273</v>
       </c>
       <c r="R98" t="n">
-        <v>6882934</v>
+        <v>6882421</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12989,22 +12963,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13019,77 +12993,74 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marcus Hansson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127315773</t>
+          <t>https://artportalen.se/Sighting/128822499</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128820534</v>
+        <v>118122325</v>
       </c>
       <c r="B99" t="n">
-        <v>58057</v>
+        <v>5179</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103031</v>
+        <v>100526</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>362267</v>
+        <v>362234</v>
       </c>
       <c r="R99" t="n">
-        <v>6882595</v>
+        <v>6882185</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -13113,22 +13084,27 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>På torrgran vid myrknat intill barrnaturskog</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13137,8 +13113,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Myrmark intill barrnaturskog</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13154,58 +13141,73 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820534</t>
+          <t>https://artportalen.se/Sighting/118122325</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118122289</v>
+        <v>127315773</v>
       </c>
       <c r="B100" t="n">
-        <v>99035</v>
+        <v>58057</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219790</v>
+        <v>103031</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>362232</v>
+        <v>363120</v>
       </c>
       <c r="R100" t="n">
-        <v>6882193</v>
+        <v>6882934</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -13229,22 +13231,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13253,86 +13255,83 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>Barrnaturskog vid myrkant</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Marcus Hansson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118122289</t>
+          <t>https://artportalen.se/Sighting/127315773</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118118517</v>
+        <v>128820534</v>
       </c>
       <c r="B101" t="n">
-        <v>97983</v>
+        <v>58057</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>362380</v>
+        <v>362267</v>
       </c>
       <c r="R101" t="n">
-        <v>6882294</v>
+        <v>6882595</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -13356,27 +13355,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Växer under gamla granar i barrnaturskog. Fuktig miljö.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13385,19 +13379,8 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13413,16 +13396,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118517</t>
+          <t>https://artportalen.se/Sighting/128820534</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118118821</v>
+        <v>118122289</v>
       </c>
       <c r="B102" t="n">
-        <v>97983</v>
+        <v>99035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13430,21 +13413,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -13458,10 +13441,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>362339</v>
+        <v>362232</v>
       </c>
       <c r="R102" t="n">
-        <v>6882268</v>
+        <v>6882193</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -13488,27 +13471,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Växer på en stor yta under gamla granar i barrnaturskog</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13528,7 +13506,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Barrnaturskog. Fjällnära</t>
+          <t>Barrnaturskog vid myrkant</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -13545,13 +13523,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118118821</t>
+          <t>https://artportalen.se/Sighting/118122289</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118119084</v>
+        <v>118118517</v>
       </c>
       <c r="B103" t="n">
         <v>97983</v>
@@ -13590,10 +13568,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>362369</v>
+        <v>362380</v>
       </c>
       <c r="R103" t="n">
-        <v>6882345</v>
+        <v>6882294</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -13625,7 +13603,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13635,7 +13613,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Växer under gamla granar i barrnaturskog. Fuktig miljö.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13655,7 +13638,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Grannaturskog. Fjällnära</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -13672,13 +13655,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118119084</t>
+          <t>https://artportalen.se/Sighting/118118517</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127171558</v>
+        <v>118118821</v>
       </c>
       <c r="B104" t="n">
         <v>97983</v>
@@ -13713,17 +13696,17 @@
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>363325</v>
+        <v>362339</v>
       </c>
       <c r="R104" t="n">
-        <v>6882909</v>
+        <v>6882268</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13747,22 +13730,27 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Växer på en stor yta under gamla granar i barrnaturskog</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13771,8 +13759,19 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Barrnaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -13788,13 +13787,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127171558</t>
+          <t>https://artportalen.se/Sighting/118118821</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127172203</v>
+        <v>118119084</v>
       </c>
       <c r="B105" t="n">
         <v>97983</v>
@@ -13829,17 +13828,17 @@
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Sälderbäcken, Storsätern (S Grövelsjön)  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>363195</v>
+        <v>362369</v>
       </c>
       <c r="R105" t="n">
-        <v>6882944</v>
+        <v>6882345</v>
       </c>
       <c r="S105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13863,22 +13862,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13887,8 +13886,19 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Grannaturskog. Fjällnära</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -13904,13 +13914,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172203</t>
+          <t>https://artportalen.se/Sighting/118119084</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127172331</v>
+        <v>127171558</v>
       </c>
       <c r="B106" t="n">
         <v>97983</v>
@@ -13949,10 +13959,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>363170</v>
+        <v>363325</v>
       </c>
       <c r="R106" t="n">
-        <v>6882973</v>
+        <v>6882909</v>
       </c>
       <c r="S106" t="n">
         <v>4</v>
@@ -13984,7 +13994,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13994,7 +14004,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14020,13 +14030,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172331</t>
+          <t>https://artportalen.se/Sighting/127171558</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128820515</v>
+        <v>127172203</v>
       </c>
       <c r="B107" t="n">
         <v>97983</v>
@@ -14058,21 +14068,17 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>362287</v>
+        <v>363195</v>
       </c>
       <c r="R107" t="n">
-        <v>6882523</v>
+        <v>6882944</v>
       </c>
       <c r="S107" t="n">
         <v>4</v>
@@ -14099,22 +14105,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14139,6 +14145,242 @@
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172203</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>127172331</v>
+      </c>
+      <c r="B108" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>363170</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6882973</v>
+      </c>
+      <c r="S108" t="n">
+        <v>4</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172331</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>128820515</v>
+      </c>
+      <c r="B109" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>362287</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6882523</v>
+      </c>
+      <c r="S109" t="n">
+        <v>4</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128820515</t>
         </is>
@@ -14252,6 +14494,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>136420582</v>
       </c>
       <c r="B15" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136420049</v>
       </c>
       <c r="B49" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>136420324</v>
       </c>
       <c r="B50" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>136420582</v>
       </c>
       <c r="B15" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136420049</v>
       </c>
       <c r="B49" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>136420324</v>
       </c>
       <c r="B50" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -2202,7 +2202,7 @@
         <v>136420582</v>
       </c>
       <c r="B15" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         <v>136420049</v>
       </c>
       <c r="B49" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>136420324</v>
       </c>
       <c r="B50" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -6733,11 +6733,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 33285-2025 artfynd.xlsx
+++ b/artfynd/A 33285-2025 artfynd.xlsx
@@ -6702,7 +6702,7 @@
         <v>136873109</v>
       </c>
       <c r="B51" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>136873218</v>
       </c>
       <c r="B52" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
